--- a/base_history_metriques_adam_train_val.xlsx
+++ b/base_history_metriques_adam_train_val.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/725bbd4577e01318/Desktop/MASTER_IA_DIT/DEVOIR_DEEP_LEARNING/cnn-catsdogs-DrameSekou/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D2BFD360D41BC101C8F050E0C0F37A01F933" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C402EC47-D91D-40EE-831C-A52E0B2C588D}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B59D2BFD360D41BC101C8F050E0C0F37A01F933" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA1F51D-71BD-4540-A1B8-4BFEBEFB22F9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -59,15 +72,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,12 +94,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -397,289 +433,293 @@
     <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.65769897762934371</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.62365830940670441</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.60094444444444439</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.64</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.61962264150943391</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>0.72848269742679683</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="J2">
+        <f>MAX(E2:E11)</f>
+        <v>0.7068888888888889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.62672042253282334</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>0.66323673470815026</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.6477222222222222</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.62288888888888894</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.58098284384995635</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>0.88642413487133986</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.60968198458353673</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.61856271055009626</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.66816666666666669</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>0.66288888888888886</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.68734112862226737</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>0.59982253771073646</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.58676518138249711</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.58213380209604904</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.68861111111111106</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>0.68488888888888888</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.6582134746404239</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.77151730257320317</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.57574938639005024</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.56583261161380349</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.69766666666666666</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>0.6975555555555556</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.68231931400571666</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.7413487133984028</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>0.56970582760704891</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>0.55745679341422183</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>0.70561111111111108</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>0.69977777777777783</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.69286629645450659</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.71960958296362021</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>0.5669518329567379</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>0.55599809259838529</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.70527777777777778</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>0.70422222222222219</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.69546802202456581</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.72848269742679683</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.56673923222223921</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.56077151446872286</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.70544444444444443</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>0.7028888888888889</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.67778208607987589</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>0.77551020408163263</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>0.56586510584089489</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>0.55641815635893077</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>0.70705555555555555</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>0.7068888888888889</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>0.68934791413527741</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>0.75510204081632648</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>0.56152711179521353</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>0.55698384454515248</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.71211111111111114</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>0.7055555555555556</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>0.68752523213564798</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>0.75554569653948533</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>

--- a/base_history_metriques_adam_train_val.xlsx
+++ b/base_history_metriques_adam_train_val.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/725bbd4577e01318/Desktop/MASTER_IA_DIT/DEVOIR_DEEP_LEARNING/cnn-catsdogs-DrameSekou/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B59D2BFD360D41BC101C8F050E0C0F37A01F933" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FA1F51D-71BD-4540-A1B8-4BFEBEFB22F9}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2B59D2BFD360D41BC101C8F050E0C0F37A01F933" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F5182D3-5A8B-4EF0-AA07-25F5BCF6A791}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -423,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
@@ -433,7 +433,7 @@
     <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -459,7 +459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -484,12 +484,8 @@
       <c r="H2" s="1">
         <v>1E-3</v>
       </c>
-      <c r="J2">
-        <f>MAX(E2:E11)</f>
-        <v>0.7068888888888889</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -515,7 +511,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -541,7 +537,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -567,7 +563,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -593,7 +589,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -619,7 +615,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -645,7 +641,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -671,7 +667,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -697,7 +693,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
